--- a/tickers/SPOT/SPOT_model.xlsx
+++ b/tickers/SPOT/SPOT_model.xlsx
@@ -1977,7 +1977,7 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>[FY25A 34.0%; fwd Bernstein-style driver bridge; 5th hike 2027 baked in per KC P1.2]</t>
+          <t>[FY25A 34.0%; FY28 37.3% TOP-DOWN anchor (CJ +170bps / Wolfe / mgmt LT band); 5th hike 2027 per KC P1.2; see GM Build tab]</t>
         </is>
       </c>
     </row>
@@ -3799,162 +3799,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lever (a) Pricing actions annualizing</t>
-        </is>
-      </c>
-      <c r="G5" s="37" t="n">
-        <v>200</v>
-      </c>
-      <c r="H5" s="37" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="37" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" s="37" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" s="37" t="n">
-        <v>20</v>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>FY28 GM = TOP-DOWN anchor: +170bps vs CJ Fig 28 | ±20bps vs Wolfe Exh 17 | inside mgmt LT band (IR Day 2030: 35-40%). NOT summed from levers.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lever (b) Music royalty inflation</t>
-        </is>
-      </c>
-      <c r="G6" s="37" t="n">
-        <v>-100</v>
-      </c>
-      <c r="H6" s="37" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I6" s="37" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J6" s="37" t="n">
-        <v>-50</v>
-      </c>
-      <c r="K6" s="37" t="n">
-        <v>-40</v>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Q1 26 Y/Y bridge (Bernstein Exh 7) — sourced current run-rate, foots 33.5% -&gt; 34.8% (+130bps):</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lever (c) Audiobook bundle allocation</t>
-        </is>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="37" t="n">
-        <v>0</v>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing +490 | Music -200 | Audiobooks -70 | SPP/Podcasts -60 | Pay/Delivery -60 | Marketplace +40</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lever (d) Marketplace (Discovery + label-side)</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="n">
-        <v>50</v>
-      </c>
-      <c r="H8" s="37" t="n">
-        <v>75</v>
-      </c>
-      <c r="I8" s="37" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="37" t="n">
-        <v>75</v>
-      </c>
-      <c r="K8" s="37" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lever (e) SPP launch costs</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H9" s="37" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="37" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lever (f) Payment / streaming delivery</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H10" s="37" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I10" s="37" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J10" s="37" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K10" s="37" t="n">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sum of levers (check)</t>
-        </is>
-      </c>
-      <c r="G11" s="38">
-        <f>SUM(G5:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="38">
-        <f>SUM(H5:H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="38">
-        <f>SUM(I5:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="38">
-        <f>SUM(J5:J10)</f>
-        <v/>
-      </c>
-      <c r="K11" s="38">
-        <f>SUM(K5:K10)</f>
-        <v/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Forward lever DIRECTION (qualitative, not summed): pricing decays (re-fed by 2027 5th hike) | music capped by 2025 renewals | audiobook eases | Marketplace accelerates | SPP rolls off | pay/delivery eases.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4342,7 +4211,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Note: Y/Y bps levers illustrate the Bernstein-style driver bridge. The model engine drives off the Premium GM and Ad-Supp GM rates set in '2. Assumptions' rows 14-15; levers here are color, not the calculation chain.</t>
+          <t>Note: Premium GM is set TOP-DOWN (FY28 37.3%, anchored vs CJ Fig 28 +170bps / Wolfe / mgmt LT band) with a sourced Q1 26 Bernstein bridge (Exh 7, foots) + qualitative forward direction (rows 5-8). Ad-Supp levers below DO foot to the rate. The engine drives off the GM rates in '2. Assumptions' rows 14-15.</t>
         </is>
       </c>
     </row>
